--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="B2" s="1" t="n">
-        <v>45981.63212962963</v>
+        <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45982</v>
+        <v>45983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45983</v>
+        <v>45984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45984</v>
+        <v>45985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45987</v>
+        <v>45988</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45988</v>
+        <v>45989</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45989</v>
+        <v>45990</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45990</v>
+        <v>45991</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45991</v>
+        <v>45992</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46010</v>
+        <v>46011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46011</v>
+        <v>46012</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46012</v>
+        <v>46013</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46013</v>
+        <v>46017</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46017</v>
+        <v>46019</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46019</v>
+        <v>46020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46022</v>
+        <v>46025</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46031</v>
+        <v>46032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46032</v>
+        <v>46033</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46033</v>
+        <v>46034</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46038</v>
+        <v>46039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46039</v>
+        <v>46040</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46040</v>
+        <v>46041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46045</v>
+        <v>46046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46046</v>
+        <v>46047</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46047</v>
+        <v>46048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46082</v>
+        <v>46083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46087</v>
+        <v>46088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46088</v>
+        <v>46089</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46089</v>
+        <v>46090</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46101</v>
+        <v>46102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46102</v>
+        <v>46103</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46103</v>
+        <v>46104</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46109</v>
+        <v>46110</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46110</v>
+        <v>46111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46114</v>
+        <v>46115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46115</v>
+        <v>46116</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46116</v>
+        <v>46117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46117</v>
+        <v>46118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46122</v>
+        <v>46123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46123</v>
+        <v>46124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46124</v>
+        <v>46125</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46129</v>
+        <v>46130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46130</v>
+        <v>46131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46131</v>
+        <v>46132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46136</v>
+        <v>46137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46137</v>
+        <v>46138</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46138</v>
+        <v>46139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46158</v>
+        <v>46159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/Översikt BURLÖV.xlsx
+++ b/Översikt BURLÖV.xlsx
@@ -567,7 +567,7 @@
         <v>45981</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>46159</v>
+        <v>46160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
